--- a/knowledge_directory/data_collection.xlsx
+++ b/knowledge_directory/data_collection.xlsx
@@ -687,7 +687,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -722,6 +722,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -730,7 +736,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -790,14 +796,14 @@
   </cellStyleXfs>
   <cellXfs count="23">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -823,8 +829,8 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -832,16 +838,16 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -850,10 +856,10 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1168,7 +1174,7 @@
     <col min="5" max="5" style="7" width="39.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1185,7 +1191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A2" s="21">
         <v>1</v>
       </c>
@@ -1202,7 +1208,7 @@
         <v>176</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A3" s="21">
         <v>2</v>
       </c>
@@ -1219,7 +1225,7 @@
         <v>180</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A4" s="21">
         <v>3</v>
       </c>
@@ -1236,7 +1242,7 @@
         <v>184</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A5" s="21">
         <v>4</v>
       </c>
@@ -1253,7 +1259,7 @@
         <v>188</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A6" s="21">
         <v>5</v>
       </c>
@@ -1270,7 +1276,7 @@
         <v>192</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A7" s="21">
         <v>6</v>
       </c>
@@ -1287,7 +1293,7 @@
         <v>196</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A8" s="21">
         <v>7</v>
       </c>
@@ -1304,7 +1310,7 @@
         <v>200</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A9" s="21">
         <v>8</v>
       </c>
@@ -1321,7 +1327,7 @@
         <v>204</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A10" s="21">
         <v>9</v>
       </c>
@@ -1338,7 +1344,7 @@
         <v>208</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A11" s="21">
         <v>10</v>
       </c>
@@ -1355,7 +1361,7 @@
         <v>212</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A12" s="21">
         <v>11</v>
       </c>
@@ -1372,7 +1378,7 @@
         <v>216</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A13" s="21">
         <v>12</v>
       </c>
@@ -1412,7 +1418,7 @@
     <col min="8" max="8" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="32.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="32.25" customFormat="1" s="1">
       <c r="A1" s="15"/>
       <c r="B1" s="16" t="s">
         <v>4</v>
@@ -1436,7 +1442,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="17" t="s">
         <v>27</v>
       </c>
@@ -1644,7 +1650,7 @@
         <v>168</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="70.5">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="17" t="s">
         <v>59</v>
       </c>
@@ -1670,7 +1676,7 @@
         <v>168</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="70.5">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="17" t="s">
         <v>63</v>
       </c>
@@ -1696,7 +1702,7 @@
         <v>169</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="70.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="17" t="s">
         <v>67</v>
       </c>
@@ -2367,7 +2373,7 @@
     <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2385,7 +2391,7 @@
       </c>
       <c r="F1" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -2403,7 +2409,7 @@
       </c>
       <c r="F2" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -2421,7 +2427,7 @@
       </c>
       <c r="F3" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -2439,7 +2445,7 @@
       </c>
       <c r="F4" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -2457,7 +2463,7 @@
       </c>
       <c r="F5" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -2475,7 +2481,7 @@
       </c>
       <c r="F6" s="13"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -2493,7 +2499,7 @@
       </c>
       <c r="F7" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -2511,7 +2517,7 @@
       </c>
       <c r="F8" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -2529,7 +2535,7 @@
       </c>
       <c r="F9" s="13"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -2547,7 +2553,7 @@
       </c>
       <c r="F10" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -2565,7 +2571,7 @@
       </c>
       <c r="F11" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -2583,7 +2589,7 @@
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -2601,7 +2607,7 @@
       </c>
       <c r="F13" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -2619,7 +2625,7 @@
       </c>
       <c r="F14" s="13"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -2637,7 +2643,7 @@
       </c>
       <c r="F15" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A16" s="8">
         <v>15</v>
       </c>
@@ -2655,7 +2661,7 @@
       </c>
       <c r="F16" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -2673,7 +2679,7 @@
       </c>
       <c r="F17" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A18" s="8">
         <v>17</v>
       </c>
@@ -2691,7 +2697,7 @@
       </c>
       <c r="F18" s="13"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -2709,7 +2715,7 @@
       </c>
       <c r="F19" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -2727,7 +2733,7 @@
       </c>
       <c r="F20" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -2745,7 +2751,7 @@
       </c>
       <c r="F21" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A22" s="8">
         <v>21</v>
       </c>
@@ -2763,7 +2769,7 @@
       </c>
       <c r="F22" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A23" s="8">
         <v>22</v>
       </c>
@@ -2781,7 +2787,7 @@
       </c>
       <c r="F23" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A24" s="8">
         <v>23</v>
       </c>
@@ -2799,7 +2805,7 @@
       </c>
       <c r="F24" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A25" s="8">
         <v>24</v>
       </c>
@@ -2817,7 +2823,7 @@
       </c>
       <c r="F25" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -2835,7 +2841,7 @@
       </c>
       <c r="F26" s="13"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -2853,7 +2859,7 @@
       </c>
       <c r="F27" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A28" s="8">
         <v>27</v>
       </c>
@@ -2871,7 +2877,7 @@
       </c>
       <c r="F28" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -2889,7 +2895,7 @@
       </c>
       <c r="F29" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -2907,7 +2913,7 @@
       </c>
       <c r="F30" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -2925,7 +2931,7 @@
       </c>
       <c r="F31" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -2943,7 +2949,7 @@
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -2961,7 +2967,7 @@
       </c>
       <c r="F33" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A34" s="8">
         <v>33</v>
       </c>
@@ -2979,7 +2985,7 @@
       </c>
       <c r="F34" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -2997,7 +3003,7 @@
       </c>
       <c r="F35" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="41.25" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="41.25" customFormat="1" s="1">
       <c r="A36" s="8">
         <v>35</v>
       </c>
@@ -3034,21 +3040,21 @@
     <col min="4" max="4" style="7" width="43.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3062,7 +3068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3076,7 +3082,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3090,7 +3096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3104,7 +3110,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3118,7 +3124,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3132,7 +3138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
